--- a/Experiments/Daz2026/JPCDMvsPOPCDM/POPvJPvCauchy/TestFits/H0_H1_parameter_comparison.xlsx
+++ b/Experiments/Daz2026/JPCDMvsPOPCDM/POPvJPvCauchy/TestFits/H0_H1_parameter_comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prefabteam_ysl/Documents/GitHub/DazExperiments/Experiments/Daz2026/JPCDMvsPOPCDM/POPvJPvCauchy/TestFits/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3B3D4034-3053-844E-85BA-1371BD6F8B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AA0327-853B-2E43-B6D1-FA063F8729B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31680" yWindow="-18520" windowWidth="27640" windowHeight="16680" xr2:uid="{64E65024-188D-5F42-9231-E271B535CA34}"/>
+    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="18060" xr2:uid="{64E65024-188D-5F42-9231-E271B535CA34}"/>
   </bookViews>
   <sheets>
     <sheet name="H0_H1_parameter_comparison" sheetId="1" r:id="rId1"/>
@@ -320,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,18 +508,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -634,6 +658,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -679,24 +746,37 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1075,4009 +1155,4079 @@
   <dimension ref="A1:AH78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="10" width="6.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="6.83203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.83203125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="6.83203125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="6.83203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="6.83203125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="6.83203125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="6.83203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="6.83203125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="6.83203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="6.83203125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="6.83203125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="6.83203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="6.83203125" style="4" customWidth="1"/>
+    <col min="26" max="26" width="6.83203125" style="5" customWidth="1"/>
+    <col min="27" max="27" width="6.83203125" style="3" customWidth="1"/>
+    <col min="28" max="28" width="6.83203125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="6.83203125" style="4" customWidth="1"/>
+    <col min="30" max="30" width="6.83203125" style="5" customWidth="1"/>
+    <col min="31" max="31" width="6.83203125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="6.83203125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="6.83203125" style="4" customWidth="1"/>
+    <col min="34" max="34" width="6.83203125" style="5" customWidth="1"/>
+    <col min="35" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>2949.83</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>2944.18</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="6">
         <v>2906.45</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>2905.42</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>6017.39</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>6073.36</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="6">
         <v>5997.89</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="7">
         <v>5995.84</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="3">
         <v>0.1</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>0.1</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="4">
         <v>0.11</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>0.1</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="3">
         <v>3.94</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="5">
         <v>5.14</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="3">
         <v>0.23</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="2">
         <v>0.22</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="4">
         <v>0.21</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="7">
         <v>0.26</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="2">
         <v>0.48</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF6">
+      <c r="AF6" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG6">
+      <c r="AG6" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH6">
+      <c r="AH6" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="3">
         <v>0.08</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>0.09</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="4">
         <v>0.1</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>0.09</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="3">
         <v>3.94</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="4">
         <v>5.04</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="5">
         <v>5.14</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="3">
         <v>0.23</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="2">
         <v>0.22</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="4">
         <v>0.21</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="7">
         <v>0.25</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="2">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH7">
+      <c r="AH7" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="3">
         <v>0.05</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>0.06</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="4">
         <v>0.06</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>0.06</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="3">
         <v>3.94</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="4">
         <v>4.74</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="5">
         <v>5.14</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="3">
         <v>0.23</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="2">
         <v>0.22</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="4">
         <v>0.21</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="7">
         <v>0.31</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="2">
         <v>0.63</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF8">
+      <c r="AF8" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG8">
+      <c r="AG8" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH8">
+      <c r="AH8" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="3">
         <v>0.16</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>0.17</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="4">
         <v>0.17</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>0.17</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="3">
         <v>3.94</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="4">
         <v>4.83</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="5">
         <v>5.14</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="3">
         <v>0.23</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="2">
         <v>0.22</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="4">
         <v>0.21</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="7">
         <v>0.31</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="2">
         <v>0.38</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH9">
+      <c r="AH9" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+    <row r="10" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="3">
         <v>0.1</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>0.11</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="4">
         <v>0.11</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="5">
         <v>0.11</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="3">
         <v>3.94</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="4">
         <v>4.95</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="5">
         <v>5.14</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="3">
         <v>0.23</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="2">
         <v>0.22</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="4">
         <v>0.21</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="2">
         <v>0.34</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG10">
+      <c r="AG10" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH10">
+      <c r="AH10" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="3">
         <v>0.05</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>0.05</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="4">
         <v>0.06</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="5">
         <v>0.05</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="3">
         <v>3.94</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="4">
         <v>4.7699999999999996</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="5">
         <v>5.14</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="3">
         <v>0.23</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="2">
         <v>0.22</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="4">
         <v>0.21</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="7">
         <v>0.31</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="2">
         <v>0.43</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH11">
+      <c r="AH11" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="3">
         <v>0.2</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>0.2</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="4">
         <v>0.21</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="5">
         <v>0.2</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="3">
         <v>3.94</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="4">
         <v>4.59</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="5">
         <v>5.14</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="3">
         <v>0.23</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="2">
         <v>0.22</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="4">
         <v>0.21</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="7">
         <v>0.35</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="2">
         <v>0.67</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG12">
+      <c r="AG12" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH12">
+      <c r="AH12" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="3">
         <v>0.08</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>0.08</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="4">
         <v>0.08</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="5">
         <v>0.08</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="3">
         <v>3.94</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="4">
         <v>4.53</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="5">
         <v>5.14</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="3">
         <v>0.23</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="2">
         <v>0.22</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="4">
         <v>0.21</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="7">
         <v>0.38</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="2">
         <v>0.52</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG13">
+      <c r="AG13" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH13">
+      <c r="AH13" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="3">
         <v>0.32</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>0.32</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="4">
         <v>0.32</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="5">
         <v>0.32</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="3">
         <v>3.94</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="4">
         <v>4.66</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="5">
         <v>5.14</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="3">
         <v>0.23</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="2">
         <v>0.22</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="4">
         <v>0.21</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="7">
         <v>0.33</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="2">
         <v>0.66</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="3">
         <v>5.52</v>
       </c>
-      <c r="AB14">
+      <c r="AB14" s="2">
         <v>5.27</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="4">
         <v>5.57</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="5">
         <v>4.88</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF14">
+      <c r="AF14" s="2">
         <v>0.47</v>
       </c>
-      <c r="AG14">
+      <c r="AG14" s="4">
         <v>0.44</v>
       </c>
-      <c r="AH14">
+      <c r="AH14" s="5">
         <v>0.55000000000000004</v>
       </c>
     </row>
+    <row r="15" spans="1:34" s="9" customFormat="1" ht="2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8"/>
+      <c r="V15" s="8"/>
+    </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="V16" s="7"/>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>1141.48</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>1089.1600000000001</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="6">
         <v>889.88</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="5">
         <v>937.51</v>
       </c>
+      <c r="V17" s="7"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="3">
         <v>2400.69</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>2363.33</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="6">
         <v>1964.76</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="5">
         <v>2060.02</v>
       </c>
+      <c r="V18" s="7"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>0.05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="5">
         <v>0.05</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="3">
         <v>7.08</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="4">
         <v>7.36</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="5">
         <v>6.16</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="3">
         <v>0.48</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="2">
         <v>0.59</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="7">
         <v>0.52</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="3">
         <v>1.6</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="2">
         <v>1.45</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB19">
+      <c r="AB19" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG19">
+      <c r="AG19" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH19">
+      <c r="AH19" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="3">
         <v>0.08</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="3">
         <v>7.08</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="4">
         <v>6.72</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="5">
         <v>6.16</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="3">
         <v>0.48</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="2">
         <v>0.59</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="3">
         <v>1.6</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="2">
         <v>1.81</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB20">
+      <c r="AB20" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG20">
+      <c r="AG20" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH20">
+      <c r="AH20" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>0.05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="4">
         <v>0.06</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="5">
         <v>0.06</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="3">
         <v>7.08</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="4">
         <v>6.35</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="5">
         <v>6.16</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="3">
         <v>0.48</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="2">
         <v>0.59</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="7">
         <v>0.6</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="3">
         <v>1.6</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="2">
         <v>1.5</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF21">
+      <c r="AF21" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG21">
+      <c r="AG21" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH21">
+      <c r="AH21" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>0.12</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="4">
         <v>0.13</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="5">
         <v>0.13</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="3">
         <v>7.08</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="4">
         <v>6.56</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="5">
         <v>6.16</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="3">
         <v>0.48</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="2">
         <v>0.59</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="3">
         <v>1.6</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="2">
         <v>1.49</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF22">
+      <c r="AF22" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG22">
+      <c r="AG22" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH22">
+      <c r="AH22" s="5">
         <v>0.2</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>0.06</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="5">
         <v>0.06</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="3">
         <v>7.08</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="4">
         <v>6.95</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="5">
         <v>6.16</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="3">
         <v>0.48</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="2">
         <v>0.59</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="3">
         <v>1.6</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="2">
         <v>1.7</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF23">
+      <c r="AF23" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG23">
+      <c r="AG23" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH23">
+      <c r="AH23" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="3">
         <v>0.06</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="2">
         <v>0.03</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="4">
         <v>0.04</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="5">
         <v>0.04</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="3">
         <v>7.08</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="4">
         <v>6.12</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="5">
         <v>6.16</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="3">
         <v>0.48</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="2">
         <v>0.59</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="7">
         <v>0.61</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="3">
         <v>1.6</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="2">
         <v>1.62</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF24">
+      <c r="AF24" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG24">
+      <c r="AG24" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH24">
+      <c r="AH24" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="2">
         <v>0.12</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="4">
         <v>0.13</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="5">
         <v>0.13</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="3">
         <v>7.08</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="4">
         <v>5.76</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="5">
         <v>6.16</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="3">
         <v>0.48</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="2">
         <v>0.59</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="7">
         <v>0.63</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="3">
         <v>1.6</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="2">
         <v>2.08</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB25">
+      <c r="AB25" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF25">
+      <c r="AF25" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG25">
+      <c r="AG25" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH25">
+      <c r="AH25" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="3">
         <v>0.19</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="2">
         <v>0.16</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="4">
         <v>0.18</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="5">
         <v>0.18</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="3">
         <v>7.08</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="4">
         <v>5.07</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="5">
         <v>6.16</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="3">
         <v>0.48</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="2">
         <v>0.59</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="7">
         <v>0.69</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="3">
         <v>1.6</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="2">
         <v>2.7</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB26">
+      <c r="AB26" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF26">
+      <c r="AF26" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG26">
+      <c r="AG26" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH26">
+      <c r="AH26" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="3">
         <v>0.33</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="2">
         <v>0.32</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="4">
         <v>0.32</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="5">
         <v>0.33</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="3">
         <v>7.08</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="2">
         <v>6.8</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="4">
         <v>5.86</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="5">
         <v>6.16</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="3">
         <v>0.48</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="2">
         <v>0.59</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="7">
         <v>0.63</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="3">
         <v>1.6</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="2">
         <v>2.04</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="4">
         <v>1.29</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="5">
         <v>1.33</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="3">
         <v>4.34</v>
       </c>
-      <c r="AB27">
+      <c r="AB27" s="2">
         <v>3.22</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="4">
         <v>3.96</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="5">
         <v>3.88</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="3">
         <v>0.33</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" s="2">
         <v>0.35</v>
       </c>
-      <c r="AG27">
+      <c r="AG27" s="4">
         <v>0.23</v>
       </c>
-      <c r="AH27">
+      <c r="AH27" s="5">
         <v>0.2</v>
       </c>
     </row>
+    <row r="28" spans="1:34" s="9" customFormat="1" ht="2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8"/>
+      <c r="V28" s="8"/>
+    </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="V29" s="7"/>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>1225.1400000000001</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>1202.96</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="4">
         <v>1093.1600000000001</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="7">
         <v>1064.8399999999999</v>
       </c>
+      <c r="V30" s="7"/>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <v>2568.02</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="2">
         <v>2590.96</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="4">
         <v>2371.36</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="7">
         <v>2314.71</v>
       </c>
+      <c r="V31" s="7"/>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="3">
         <v>0.04</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="4">
         <v>0.08</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="5">
         <v>0.06</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="3">
         <v>4.88</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="4">
         <v>6.22</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="5">
         <v>5.35</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="3">
         <v>0.39</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="2">
         <v>0.37</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="4">
         <v>0.34</v>
       </c>
-      <c r="V32">
+      <c r="V32" s="7">
         <v>0.34</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="2">
         <v>1.21</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z32">
+      <c r="Z32" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA32">
+      <c r="AA32" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB32">
+      <c r="AB32" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF32">
+      <c r="AF32" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG32">
+      <c r="AG32" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH32">
+      <c r="AH32" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="3">
         <v>0.09</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="2">
         <v>0.11</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="4">
         <v>0.12</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="5">
         <v>0.11</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="3">
         <v>4.88</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="4">
         <v>5.59</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="5">
         <v>5.35</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="3">
         <v>0.39</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="2">
         <v>0.37</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="4">
         <v>0.34</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="7">
         <v>0.37</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z33">
+      <c r="Z33" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA33">
+      <c r="AA33" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB33">
+      <c r="AB33" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC33">
+      <c r="AC33" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD33">
+      <c r="AD33" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE33">
+      <c r="AE33" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF33">
+      <c r="AF33" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG33">
+      <c r="AG33" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH33">
+      <c r="AH33" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="3">
         <v>0.04</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="2">
         <v>0.06</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="4">
         <v>0.08</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="5">
         <v>0.06</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="3">
         <v>4.88</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="4">
         <v>6.1</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="5">
         <v>5.35</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="3">
         <v>0.39</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="2">
         <v>0.37</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="4">
         <v>0.34</v>
       </c>
-      <c r="V34">
+      <c r="V34" s="7">
         <v>0.34</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="2">
         <v>1.1299999999999999</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z34">
+      <c r="Z34" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA34">
+      <c r="AA34" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB34">
+      <c r="AB34" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC34">
+      <c r="AC34" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD34">
+      <c r="AD34" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE34">
+      <c r="AE34" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF34">
+      <c r="AF34" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG34">
+      <c r="AG34" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH34">
+      <c r="AH34" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="3">
         <v>0.1</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="2">
         <v>0.12</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="4">
         <v>0.13</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="5">
         <v>0.13</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="3">
         <v>4.88</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="4">
         <v>5.53</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="5">
         <v>5.35</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="3">
         <v>0.39</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="2">
         <v>0.37</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="4">
         <v>0.34</v>
       </c>
-      <c r="V35">
+      <c r="V35" s="7">
         <v>0.39</v>
       </c>
-      <c r="W35">
+      <c r="W35" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="2">
         <v>1.05</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z35">
+      <c r="Z35" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA35">
+      <c r="AA35" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB35">
+      <c r="AB35" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC35">
+      <c r="AC35" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD35">
+      <c r="AD35" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE35">
+      <c r="AE35" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF35">
+      <c r="AF35" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG35">
+      <c r="AG35" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH35">
+      <c r="AH35" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="3">
         <v>0.09</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="2">
         <v>0.11</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="4">
         <v>0.12</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="5">
         <v>0.11</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="3">
         <v>4.88</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="4">
         <v>5.44</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="5">
         <v>5.35</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="3">
         <v>0.39</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="2">
         <v>0.37</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="4">
         <v>0.34</v>
       </c>
-      <c r="V36">
+      <c r="V36" s="7">
         <v>0.39</v>
       </c>
-      <c r="W36">
+      <c r="W36" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="2">
         <v>0.98</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z36">
+      <c r="Z36" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA36">
+      <c r="AA36" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB36">
+      <c r="AB36" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC36">
+      <c r="AC36" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD36">
+      <c r="AD36" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE36">
+      <c r="AE36" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF36">
+      <c r="AF36" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG36">
+      <c r="AG36" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH36">
+      <c r="AH36" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="3">
         <v>0.03</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="2">
         <v>0.04</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="4">
         <v>0.05</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="5">
         <v>0.04</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="3">
         <v>4.88</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="4">
         <v>5.73</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="5">
         <v>5.35</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="3">
         <v>0.39</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="2">
         <v>0.37</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="4">
         <v>0.34</v>
       </c>
-      <c r="V37">
+      <c r="V37" s="7">
         <v>0.37</v>
       </c>
-      <c r="W37">
+      <c r="W37" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X37">
+      <c r="X37" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z37">
+      <c r="Z37" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA37">
+      <c r="AA37" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB37">
+      <c r="AB37" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC37">
+      <c r="AC37" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD37">
+      <c r="AD37" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE37">
+      <c r="AE37" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF37">
+      <c r="AF37" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG37">
+      <c r="AG37" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH37">
+      <c r="AH37" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="3">
         <v>0.13</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="2">
         <v>0.15</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="4">
         <v>0.16</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="5">
         <v>0.16</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="3">
         <v>4.88</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="4">
         <v>5.16</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="5">
         <v>5.35</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="3">
         <v>0.39</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="2">
         <v>0.37</v>
       </c>
-      <c r="U38">
+      <c r="U38" s="4">
         <v>0.34</v>
       </c>
-      <c r="V38">
+      <c r="V38" s="7">
         <v>0.43</v>
       </c>
-      <c r="W38">
+      <c r="W38" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X38">
+      <c r="X38" s="2">
         <v>1.03</v>
       </c>
-      <c r="Y38">
+      <c r="Y38" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z38">
+      <c r="Z38" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA38">
+      <c r="AA38" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB38">
+      <c r="AB38" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC38">
+      <c r="AC38" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD38">
+      <c r="AD38" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE38">
+      <c r="AE38" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF38">
+      <c r="AF38" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG38">
+      <c r="AG38" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH38">
+      <c r="AH38" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="3">
         <v>0.05</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="2">
         <v>0.06</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="3">
         <v>4.88</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="5">
         <v>5.35</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="3">
         <v>0.39</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="2">
         <v>0.37</v>
       </c>
-      <c r="U39">
+      <c r="U39" s="4">
         <v>0.34</v>
       </c>
-      <c r="V39">
+      <c r="V39" s="7">
         <v>0.45</v>
       </c>
-      <c r="W39">
+      <c r="W39" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X39">
+      <c r="X39" s="2">
         <v>0.99</v>
       </c>
-      <c r="Y39">
+      <c r="Y39" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z39">
+      <c r="Z39" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA39">
+      <c r="AA39" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB39">
+      <c r="AB39" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC39">
+      <c r="AC39" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD39">
+      <c r="AD39" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE39">
+      <c r="AE39" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF39">
+      <c r="AF39" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG39">
+      <c r="AG39" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH39">
+      <c r="AH39" s="5">
         <v>0.19</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="3">
         <v>0.16</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="2">
         <v>0.18</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="4">
         <v>0.18</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="5">
         <v>0.18</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="3">
         <v>4.88</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="2">
         <v>5.17</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="4">
         <v>4.99</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="5">
         <v>5.35</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="3">
         <v>0.39</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="2">
         <v>0.37</v>
       </c>
-      <c r="U40">
+      <c r="U40" s="4">
         <v>0.34</v>
       </c>
-      <c r="V40">
+      <c r="V40" s="7">
         <v>0.44</v>
       </c>
-      <c r="W40">
+      <c r="W40" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="2">
         <v>1.04</v>
       </c>
-      <c r="Y40">
+      <c r="Y40" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z40">
+      <c r="Z40" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="AA40">
+      <c r="AA40" s="3">
         <v>2.5</v>
       </c>
-      <c r="AB40">
+      <c r="AB40" s="2">
         <v>3.02</v>
       </c>
-      <c r="AC40">
+      <c r="AC40" s="4">
         <v>3.25</v>
       </c>
-      <c r="AD40">
+      <c r="AD40" s="5">
         <v>3.01</v>
       </c>
-      <c r="AE40">
+      <c r="AE40" s="3">
         <v>0.24</v>
       </c>
-      <c r="AF40">
+      <c r="AF40" s="2">
         <v>0.19</v>
       </c>
-      <c r="AG40">
+      <c r="AG40" s="4">
         <v>0.21</v>
       </c>
-      <c r="AH40">
+      <c r="AH40" s="5">
         <v>0.19</v>
       </c>
     </row>
+    <row r="41" spans="1:34" s="9" customFormat="1" ht="2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="8"/>
+      <c r="V41" s="8"/>
+    </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="V42" s="7"/>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>2811.68</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>2802.19</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>2759.13</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="7">
         <v>2747.5</v>
       </c>
+      <c r="V43" s="7"/>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>5741.1</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="2">
         <v>5789.4</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="4">
         <v>5703.29</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="7">
         <v>5680.02</v>
       </c>
+      <c r="V44" s="7"/>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="3">
         <v>0.09</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="2">
         <v>0.09</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="4">
         <v>0.08</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="5">
         <v>0.08</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="3">
         <v>5.4</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="4">
         <v>5.66</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="3">
         <v>0.13</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U45">
+      <c r="U45" s="4">
         <v>0.21</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="7">
         <v>0.21</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="3">
         <v>0.89</v>
       </c>
-      <c r="X45">
+      <c r="X45" s="2">
         <v>1.1299999999999999</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z45">
+      <c r="Z45" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA45">
+      <c r="AA45" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB45">
+      <c r="AB45" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC45">
+      <c r="AC45" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD45">
+      <c r="AD45" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE45">
+      <c r="AE45" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF45">
+      <c r="AF45" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG45">
+      <c r="AG45" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH45">
+      <c r="AH45" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="3">
         <v>0.1</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="2">
         <v>0.09</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="4">
         <v>0.09</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="5">
         <v>0.09</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="20">
         <v>5.4</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="4">
         <v>5.71</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="3">
         <v>0.13</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U46">
+      <c r="U46" s="4">
         <v>0.21</v>
       </c>
-      <c r="V46">
+      <c r="V46" s="7">
         <v>0.22</v>
       </c>
-      <c r="W46">
+      <c r="W46" s="3">
         <v>0.89</v>
       </c>
-      <c r="X46">
+      <c r="X46" s="2">
         <v>1.08</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z46">
+      <c r="Z46" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA46">
+      <c r="AA46" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB46">
+      <c r="AB46" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC46">
+      <c r="AC46" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD46">
+      <c r="AD46" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE46">
+      <c r="AE46" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF46">
+      <c r="AF46" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG46">
+      <c r="AG46" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH46">
+      <c r="AH46" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="3">
         <v>0.06</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="2">
         <v>0.06</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="4">
         <v>0.05</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="5">
         <v>0.05</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="21">
         <v>5.4</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="4">
         <v>5.54</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="3">
         <v>0.13</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U47">
+      <c r="U47" s="4">
         <v>0.21</v>
       </c>
-      <c r="V47">
+      <c r="V47" s="7">
         <v>0.24</v>
       </c>
-      <c r="W47">
+      <c r="W47" s="3">
         <v>0.89</v>
       </c>
-      <c r="X47">
+      <c r="X47" s="2">
         <v>0.99</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z47">
+      <c r="Z47" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA47">
+      <c r="AA47" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB47">
+      <c r="AB47" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC47">
+      <c r="AC47" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD47">
+      <c r="AD47" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE47">
+      <c r="AE47" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF47">
+      <c r="AF47" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG47">
+      <c r="AG47" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH47">
+      <c r="AH47" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="3">
         <v>0.21</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="2">
         <v>0.21</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="4">
         <v>0.21</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="5">
         <v>0.21</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="3">
         <v>5.4</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="4">
         <v>5.41</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="3">
         <v>0.13</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U48">
+      <c r="U48" s="4">
         <v>0.21</v>
       </c>
-      <c r="V48">
+      <c r="V48" s="7">
         <v>0.25</v>
       </c>
-      <c r="W48">
+      <c r="W48" s="3">
         <v>0.89</v>
       </c>
-      <c r="X48">
+      <c r="X48" s="2">
         <v>1.0900000000000001</v>
       </c>
-      <c r="Y48">
+      <c r="Y48" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z48">
+      <c r="Z48" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA48">
+      <c r="AA48" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB48">
+      <c r="AB48" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC48">
+      <c r="AC48" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD48">
+      <c r="AD48" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE48">
+      <c r="AE48" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF48">
+      <c r="AF48" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG48">
+      <c r="AG48" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH48">
+      <c r="AH48" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="3">
         <v>0.1</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="2">
         <v>0.09</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="4">
         <v>0.09</v>
       </c>
-      <c r="N49">
+      <c r="N49" s="5">
         <v>0.09</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="3">
         <v>5.4</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="4">
         <v>5.51</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="3">
         <v>0.13</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U49">
+      <c r="U49" s="4">
         <v>0.21</v>
       </c>
-      <c r="V49">
+      <c r="V49" s="7">
         <v>0.24</v>
       </c>
-      <c r="W49">
+      <c r="W49" s="3">
         <v>0.89</v>
       </c>
-      <c r="X49">
+      <c r="X49" s="2">
         <v>0.97</v>
       </c>
-      <c r="Y49">
+      <c r="Y49" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z49">
+      <c r="Z49" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA49">
+      <c r="AA49" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB49">
+      <c r="AB49" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC49">
+      <c r="AC49" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD49">
+      <c r="AD49" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE49">
+      <c r="AE49" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF49">
+      <c r="AF49" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG49">
+      <c r="AG49" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH49">
+      <c r="AH49" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="3">
         <v>0.06</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="2">
         <v>0.06</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="4">
         <v>0.05</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="5">
         <v>0.05</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="3">
         <v>5.4</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="4">
         <v>5.2</v>
       </c>
-      <c r="R50">
+      <c r="R50" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S50">
+      <c r="S50" s="3">
         <v>0.13</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U50">
+      <c r="U50" s="4">
         <v>0.21</v>
       </c>
-      <c r="V50">
+      <c r="V50" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="W50">
+      <c r="W50" s="3">
         <v>0.89</v>
       </c>
-      <c r="X50">
+      <c r="X50" s="2">
         <v>0.88</v>
       </c>
-      <c r="Y50">
+      <c r="Y50" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z50">
+      <c r="Z50" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA50">
+      <c r="AA50" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB50">
+      <c r="AB50" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC50">
+      <c r="AC50" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD50">
+      <c r="AD50" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE50">
+      <c r="AE50" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF50">
+      <c r="AF50" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG50">
+      <c r="AG50" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH50">
+      <c r="AH50" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="2">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="4">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="5">
         <v>0.28000000000000003</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="3">
         <v>5.4</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="4">
         <v>5.37</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="3">
         <v>0.13</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U51">
+      <c r="U51" s="4">
         <v>0.21</v>
       </c>
-      <c r="V51">
+      <c r="V51" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="W51">
+      <c r="W51" s="3">
         <v>0.89</v>
       </c>
-      <c r="X51">
+      <c r="X51" s="2">
         <v>0.85</v>
       </c>
-      <c r="Y51">
+      <c r="Y51" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z51">
+      <c r="Z51" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA51">
+      <c r="AA51" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB51">
+      <c r="AB51" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC51">
+      <c r="AC51" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD51">
+      <c r="AD51" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE51">
+      <c r="AE51" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF51">
+      <c r="AF51" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG51">
+      <c r="AG51" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH51">
+      <c r="AH51" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="3">
         <v>0.12</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="2">
         <v>0.12</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="4">
         <v>0.12</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="5">
         <v>0.12</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="3">
         <v>5.4</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="4">
         <v>4.96</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S52">
+      <c r="S52" s="3">
         <v>0.13</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U52">
+      <c r="U52" s="4">
         <v>0.21</v>
       </c>
-      <c r="V52">
+      <c r="V52" s="7">
         <v>0.32</v>
       </c>
-      <c r="W52">
+      <c r="W52" s="3">
         <v>0.89</v>
       </c>
-      <c r="X52">
+      <c r="X52" s="2">
         <v>1.07</v>
       </c>
-      <c r="Y52">
+      <c r="Y52" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z52">
+      <c r="Z52" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA52">
+      <c r="AA52" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB52">
+      <c r="AB52" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC52">
+      <c r="AC52" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD52">
+      <c r="AD52" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE52">
+      <c r="AE52" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF52">
+      <c r="AF52" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG52">
+      <c r="AG52" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH52">
+      <c r="AH52" s="5">
         <v>0.08</v>
       </c>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="3">
         <v>0.55000000000000004</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="4">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="3">
         <v>5.4</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="2">
         <v>5.54</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="4">
         <v>5.13</v>
       </c>
-      <c r="R53">
+      <c r="R53" s="5">
         <v>5.1100000000000003</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="3">
         <v>0.13</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U53">
+      <c r="U53" s="4">
         <v>0.21</v>
       </c>
-      <c r="V53">
+      <c r="V53" s="7">
         <v>0.31</v>
       </c>
-      <c r="W53">
+      <c r="W53" s="3">
         <v>0.89</v>
       </c>
-      <c r="X53">
+      <c r="X53" s="2">
         <v>0.92</v>
       </c>
-      <c r="Y53">
+      <c r="Y53" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z53">
+      <c r="Z53" s="5">
         <v>0.82</v>
       </c>
-      <c r="AA53">
+      <c r="AA53" s="3">
         <v>5.75</v>
       </c>
-      <c r="AB53">
+      <c r="AB53" s="2">
         <v>5.49</v>
       </c>
-      <c r="AC53">
+      <c r="AC53" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="AD53">
+      <c r="AD53" s="5">
         <v>5.43</v>
       </c>
-      <c r="AE53">
+      <c r="AE53" s="3">
         <v>0.21</v>
       </c>
-      <c r="AF53">
+      <c r="AF53" s="2">
         <v>0.27</v>
       </c>
-      <c r="AG53">
+      <c r="AG53" s="4">
         <v>0.25</v>
       </c>
-      <c r="AH53">
+      <c r="AH53" s="5">
         <v>0.08</v>
       </c>
     </row>
+    <row r="54" spans="1:34" s="9" customFormat="1" ht="2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8"/>
+      <c r="V54" s="8"/>
+    </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="V55" s="7"/>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="3">
         <v>2463.02</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <v>2448.9699999999998</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="6">
         <v>2233.88</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="5">
         <v>2248.67</v>
       </c>
+      <c r="V56" s="7"/>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <v>5043.8</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="2">
         <v>5082.9799999999996</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="6">
         <v>4652.8</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="5">
         <v>4682.38</v>
       </c>
+      <c r="V57" s="7"/>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="3">
         <v>0.09</v>
       </c>
-      <c r="L58">
+      <c r="L58" s="2">
         <v>0.08</v>
       </c>
-      <c r="M58">
+      <c r="M58" s="4">
         <v>0.1</v>
       </c>
-      <c r="N58">
+      <c r="N58" s="5">
         <v>0.08</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="4">
         <v>5.37</v>
       </c>
-      <c r="R58">
+      <c r="R58" s="5">
         <v>4.58</v>
       </c>
-      <c r="S58">
+      <c r="S58" s="3">
         <v>0.17</v>
       </c>
-      <c r="T58">
+      <c r="T58" s="2">
         <v>0.23</v>
       </c>
-      <c r="U58">
+      <c r="U58" s="4">
         <v>0.17</v>
       </c>
-      <c r="V58">
+      <c r="V58" s="7">
         <v>0.21</v>
       </c>
-      <c r="W58">
+      <c r="W58" s="3">
         <v>0.36</v>
       </c>
-      <c r="X58">
+      <c r="X58" s="2">
         <v>0.19</v>
       </c>
-      <c r="Y58">
+      <c r="Y58" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z58">
+      <c r="Z58" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA58">
+      <c r="AA58" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB58">
+      <c r="AB58" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC58">
+      <c r="AC58" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD58">
+      <c r="AD58" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE58">
+      <c r="AE58" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF58">
+      <c r="AF58" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG58">
+      <c r="AG58" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH58">
+      <c r="AH58" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="3">
         <v>0.15</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="2">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="4">
         <v>0.15</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="4">
         <v>4.99</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="5">
         <v>4.58</v>
       </c>
-      <c r="S59">
+      <c r="S59" s="3">
         <v>0.17</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="2">
         <v>0.23</v>
       </c>
-      <c r="U59">
+      <c r="U59" s="4">
         <v>0.17</v>
       </c>
-      <c r="V59">
+      <c r="V59" s="7">
         <v>0.27</v>
       </c>
-      <c r="W59">
+      <c r="W59" s="3">
         <v>0.36</v>
       </c>
-      <c r="X59">
+      <c r="X59" s="2">
         <v>0.16</v>
       </c>
-      <c r="Y59">
+      <c r="Y59" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z59">
+      <c r="Z59" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA59">
+      <c r="AA59" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB59">
+      <c r="AB59" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC59">
+      <c r="AC59" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD59">
+      <c r="AD59" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE59">
+      <c r="AE59" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF59">
+      <c r="AF59" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG59">
+      <c r="AG59" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH59">
+      <c r="AH59" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="3">
         <v>0.04</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="2">
         <v>0.02</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="4">
         <v>0.05</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="5">
         <v>0.03</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="4">
         <v>5.15</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="5">
         <v>4.58</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="3">
         <v>0.17</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="2">
         <v>0.23</v>
       </c>
-      <c r="U60">
+      <c r="U60" s="4">
         <v>0.17</v>
       </c>
-      <c r="V60">
+      <c r="V60" s="7">
         <v>0.24</v>
       </c>
-      <c r="W60">
+      <c r="W60" s="3">
         <v>0.36</v>
       </c>
-      <c r="X60">
+      <c r="X60" s="2">
         <v>0.12</v>
       </c>
-      <c r="Y60">
+      <c r="Y60" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z60">
+      <c r="Z60" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA60">
+      <c r="AA60" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB60">
+      <c r="AB60" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC60">
+      <c r="AC60" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD60">
+      <c r="AD60" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE60">
+      <c r="AE60" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF60">
+      <c r="AF60" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG60">
+      <c r="AG60" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH60">
+      <c r="AH60" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="3">
         <v>0.2</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="2">
         <v>0.19</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="4">
         <v>0.2</v>
       </c>
-      <c r="N61">
+      <c r="N61" s="5">
         <v>0.2</v>
       </c>
-      <c r="O61">
+      <c r="O61" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="4">
         <v>4.93</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="5">
         <v>4.58</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="3">
         <v>0.17</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="2">
         <v>0.23</v>
       </c>
-      <c r="U61">
+      <c r="U61" s="4">
         <v>0.17</v>
       </c>
-      <c r="V61">
+      <c r="V61" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="W61">
+      <c r="W61" s="3">
         <v>0.36</v>
       </c>
-      <c r="X61">
+      <c r="X61" s="2">
         <v>0.1</v>
       </c>
-      <c r="Y61">
+      <c r="Y61" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z61">
+      <c r="Z61" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA61">
+      <c r="AA61" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB61">
+      <c r="AB61" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC61">
+      <c r="AC61" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD61">
+      <c r="AD61" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE61">
+      <c r="AE61" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF61">
+      <c r="AF61" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG61">
+      <c r="AG61" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH61">
+      <c r="AH61" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="3">
         <v>0.16</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="2">
         <v>0.15</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="4">
         <v>0.16</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="5">
         <v>0.15</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q62">
+      <c r="Q62" s="4">
         <v>4.8099999999999996</v>
       </c>
-      <c r="R62">
+      <c r="R62" s="5">
         <v>4.58</v>
       </c>
-      <c r="S62">
+      <c r="S62" s="3">
         <v>0.17</v>
       </c>
-      <c r="T62">
+      <c r="T62" s="2">
         <v>0.23</v>
       </c>
-      <c r="U62">
+      <c r="U62" s="4">
         <v>0.17</v>
       </c>
-      <c r="V62">
+      <c r="V62" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="W62">
+      <c r="W62" s="3">
         <v>0.36</v>
       </c>
-      <c r="X62">
+      <c r="X62" s="2">
         <v>0.22</v>
       </c>
-      <c r="Y62">
+      <c r="Y62" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z62">
+      <c r="Z62" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA62">
+      <c r="AA62" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB62">
+      <c r="AB62" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC62">
+      <c r="AC62" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD62">
+      <c r="AD62" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE62">
+      <c r="AE62" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF62">
+      <c r="AF62" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG62">
+      <c r="AG62" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH62">
+      <c r="AH62" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="3">
         <v>0.04</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="2">
         <v>0.03</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="4">
         <v>0.04</v>
       </c>
-      <c r="N63">
+      <c r="N63" s="5">
         <v>0.03</v>
       </c>
-      <c r="O63">
+      <c r="O63" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="4">
         <v>5.0199999999999996</v>
       </c>
-      <c r="R63">
+      <c r="R63" s="5">
         <v>4.58</v>
       </c>
-      <c r="S63">
+      <c r="S63" s="3">
         <v>0.17</v>
       </c>
-      <c r="T63">
+      <c r="T63" s="2">
         <v>0.23</v>
       </c>
-      <c r="U63">
+      <c r="U63" s="4">
         <v>0.17</v>
       </c>
-      <c r="V63">
+      <c r="V63" s="7">
         <v>0.25</v>
       </c>
-      <c r="W63">
+      <c r="W63" s="3">
         <v>0.36</v>
       </c>
-      <c r="X63">
+      <c r="X63" s="2">
         <v>0.34</v>
       </c>
-      <c r="Y63">
+      <c r="Y63" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z63">
+      <c r="Z63" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA63">
+      <c r="AA63" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB63">
+      <c r="AB63" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC63">
+      <c r="AC63" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD63">
+      <c r="AD63" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE63">
+      <c r="AE63" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF63">
+      <c r="AF63" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG63">
+      <c r="AG63" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH63">
+      <c r="AH63" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="3">
         <v>0.4</v>
       </c>
-      <c r="L64">
+      <c r="L64" s="2">
         <v>0.39</v>
       </c>
-      <c r="M64">
+      <c r="M64" s="4">
         <v>0.4</v>
       </c>
-      <c r="N64">
+      <c r="N64" s="5">
         <v>0.4</v>
       </c>
-      <c r="O64">
+      <c r="O64" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q64">
+      <c r="Q64" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R64">
+      <c r="R64" s="5">
         <v>4.58</v>
       </c>
-      <c r="S64">
+      <c r="S64" s="3">
         <v>0.17</v>
       </c>
-      <c r="T64">
+      <c r="T64" s="2">
         <v>0.23</v>
       </c>
-      <c r="U64">
+      <c r="U64" s="4">
         <v>0.17</v>
       </c>
-      <c r="V64">
+      <c r="V64" s="7">
         <v>0.4</v>
       </c>
-      <c r="W64">
+      <c r="W64" s="3">
         <v>0.36</v>
       </c>
-      <c r="X64">
+      <c r="X64" s="2">
         <v>0.54</v>
       </c>
-      <c r="Y64">
+      <c r="Y64" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z64">
+      <c r="Z64" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA64">
+      <c r="AA64" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB64">
+      <c r="AB64" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC64">
+      <c r="AC64" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD64">
+      <c r="AD64" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE64">
+      <c r="AE64" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF64">
+      <c r="AF64" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG64">
+      <c r="AG64" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH64">
+      <c r="AH64" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K65">
+      <c r="K65" s="3">
         <v>0.12</v>
       </c>
-      <c r="L65">
+      <c r="L65" s="2">
         <v>0.11</v>
       </c>
-      <c r="M65">
+      <c r="M65" s="4">
         <v>0.12</v>
       </c>
-      <c r="N65">
+      <c r="N65" s="5">
         <v>0.12</v>
       </c>
-      <c r="O65">
+      <c r="O65" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q65">
+      <c r="Q65" s="4">
         <v>4.37</v>
       </c>
-      <c r="R65">
+      <c r="R65" s="5">
         <v>4.58</v>
       </c>
-      <c r="S65">
+      <c r="S65" s="3">
         <v>0.17</v>
       </c>
-      <c r="T65">
+      <c r="T65" s="2">
         <v>0.23</v>
       </c>
-      <c r="U65">
+      <c r="U65" s="4">
         <v>0.17</v>
       </c>
-      <c r="V65">
+      <c r="V65" s="7">
         <v>0.38</v>
       </c>
-      <c r="W65">
+      <c r="W65" s="3">
         <v>0.36</v>
       </c>
-      <c r="X65">
+      <c r="X65" s="2">
         <v>0.61</v>
       </c>
-      <c r="Y65">
+      <c r="Y65" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z65">
+      <c r="Z65" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA65">
+      <c r="AA65" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB65">
+      <c r="AB65" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC65">
+      <c r="AC65" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD65">
+      <c r="AD65" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE65">
+      <c r="AE65" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF65">
+      <c r="AF65" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG65">
+      <c r="AG65" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH65">
+      <c r="AH65" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="3">
         <v>0.52</v>
       </c>
-      <c r="L66">
+      <c r="L66" s="2">
         <v>0.52</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="4">
         <v>0.52</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="5">
         <v>0.52</v>
       </c>
-      <c r="O66">
+      <c r="O66" s="3">
         <v>4.8099999999999996</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="2">
         <v>4.66</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="R66">
+      <c r="R66" s="5">
         <v>4.58</v>
       </c>
-      <c r="S66">
+      <c r="S66" s="3">
         <v>0.17</v>
       </c>
-      <c r="T66">
+      <c r="T66" s="2">
         <v>0.23</v>
       </c>
-      <c r="U66">
+      <c r="U66" s="4">
         <v>0.17</v>
       </c>
-      <c r="V66">
+      <c r="V66" s="7">
         <v>0.39</v>
       </c>
-      <c r="W66">
+      <c r="W66" s="3">
         <v>0.36</v>
       </c>
-      <c r="X66">
+      <c r="X66" s="2">
         <v>0.47</v>
       </c>
-      <c r="Y66">
+      <c r="Y66" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z66">
+      <c r="Z66" s="5">
         <v>0.13</v>
       </c>
-      <c r="AA66">
+      <c r="AA66" s="3">
         <v>4.91</v>
       </c>
-      <c r="AB66">
+      <c r="AB66" s="2">
         <v>4.3</v>
       </c>
-      <c r="AC66">
+      <c r="AC66" s="4">
         <v>4.9400000000000004</v>
       </c>
-      <c r="AD66">
+      <c r="AD66" s="5">
         <v>4.7</v>
       </c>
-      <c r="AE66">
+      <c r="AE66" s="3">
         <v>0.22</v>
       </c>
-      <c r="AF66">
+      <c r="AF66" s="2">
         <v>0.26</v>
       </c>
-      <c r="AG66">
+      <c r="AG66" s="4">
         <v>0.22</v>
       </c>
-      <c r="AH66">
+      <c r="AH66" s="5">
         <v>0.1</v>
       </c>
     </row>
+    <row r="68" spans="1:34" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8"/>
+    </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2" t="s">
+      <c r="D69" s="10"/>
+      <c r="E69" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="1:34" s="3" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="3" t="s">
+      <c r="F69" s="10"/>
+    </row>
+    <row r="70" spans="1:34" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="11"/>
+      <c r="B70" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4" t="s">
+      <c r="D70" s="13"/>
+      <c r="E70" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="4"/>
-    </row>
-    <row r="71" spans="1:34" s="5" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="5" t="s">
+      <c r="F70" s="13"/>
+    </row>
+    <row r="71" spans="1:34" s="15" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="14"/>
+      <c r="B71" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6" t="s">
+      <c r="D71" s="16"/>
+      <c r="E71" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="1:34" s="7" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="7" t="s">
+      <c r="F71" s="16"/>
+    </row>
+    <row r="72" spans="1:34" s="18" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="17"/>
+      <c r="B72" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8" t="s">
+      <c r="D72" s="19"/>
+      <c r="E72" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F72" s="8"/>
-    </row>
-    <row r="73" spans="1:34" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="3" t="s">
+      <c r="F72" s="19"/>
+    </row>
+    <row r="73" spans="1:34" s="12" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4" t="s">
+      <c r="D73" s="13"/>
+      <c r="E73" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="4"/>
-    </row>
-    <row r="74" spans="1:34" s="5" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="5" t="s">
+      <c r="F73" s="13"/>
+    </row>
+    <row r="74" spans="1:34" s="15" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="14"/>
+      <c r="B74" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6" t="s">
+      <c r="D74" s="16"/>
+      <c r="E74" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" spans="1:34" s="7" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="7" t="s">
+      <c r="F74" s="16"/>
+    </row>
+    <row r="75" spans="1:34" s="18" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="17"/>
+      <c r="B75" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8" t="s">
+      <c r="D75" s="19"/>
+      <c r="E75" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76" spans="1:34" s="5" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="5" t="s">
+      <c r="F75" s="19"/>
+    </row>
+    <row r="76" spans="1:34" s="15" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="14"/>
+      <c r="B76" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6" t="s">
+      <c r="D76" s="16"/>
+      <c r="E76" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:34" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="7" t="s">
+      <c r="F76" s="16"/>
+    </row>
+    <row r="77" spans="1:34" s="18" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="17"/>
+      <c r="B77" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8" t="s">
+      <c r="D77" s="19"/>
+      <c r="E77" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F77" s="8"/>
-    </row>
-    <row r="78" spans="1:34" s="3" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="3" t="s">
+      <c r="F77" s="19"/>
+    </row>
+    <row r="78" spans="1:34" s="12" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C69:D69"/>
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="C76:D76"/>
     <mergeCell ref="C77:D77"/>
@@ -5092,7 +5242,11 @@
     <mergeCell ref="C72:D72"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E69:F69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
